--- a/outputs/powerbi/PowerBI_data.xlsx
+++ b/outputs/powerbi/PowerBI_data.xlsx
@@ -70131,7 +70131,7 @@
         <v>0.4442</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.89</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="3">
@@ -70163,7 +70163,7 @@
         <v>0.4396</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.19</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="4">
@@ -70195,7 +70195,7 @@
         <v>0.4018</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>27.92</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="5">
@@ -70227,7 +70227,7 @@
         <v>0.1798</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20.72</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="6">
@@ -70259,7 +70259,7 @@
         <v>0.1392</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="7">
@@ -70291,7 +70291,7 @@
         <v>0.0818</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="8">
@@ -70323,7 +70323,7 @@
         <v>0.1313</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.89</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="9">
@@ -70355,7 +70355,7 @@
         <v>-0.1123</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>27.92</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="10">
@@ -70387,7 +70387,7 @@
         <v>-0.2668</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="11">
@@ -70419,7 +70419,7 @@
         <v>-0.3911</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="12">
@@ -70451,7 +70451,7 @@
         <v>-0.3945</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20.72</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="13">
@@ -70483,7 +70483,7 @@
         <v>-0.6235000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.19</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="14">
@@ -70515,7 +70515,7 @@
         <v>0.9147</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -70547,7 +70547,7 @@
         <v>0.8773</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>21.15</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="16">
@@ -70579,7 +70579,7 @@
         <v>0.837</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.5</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="17">
@@ -70611,7 +70611,7 @@
         <v>0.8279</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.34</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="18">
@@ -70643,7 +70643,7 @@
         <v>0.3554</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19">
@@ -70707,7 +70707,7 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21.15</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="21">
@@ -70739,7 +70739,7 @@
         <v>0.6235000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="22">
@@ -70771,7 +70771,7 @@
         <v>0.5308</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>16.5</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="23">
@@ -70803,7 +70803,7 @@
         <v>0.3834</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2.34</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="24">
@@ -70867,7 +70867,7 @@
         <v>-0.0771</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -71631,16 +71631,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.7107</v>
+        <v>1.7785</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.9117</v>
+        <v>0.9045</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.9773</v>
+        <v>3.2004</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5998</v>
+        <v>0.5376</v>
       </c>
     </row>
     <row r="4">
@@ -71655,16 +71655,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.4586</v>
+        <v>1.4087</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9358</v>
+        <v>0.9401</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.3815</v>
+        <v>2.2797</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7439</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="5">
